--- a/Мои БАГ-РЕПОРТЫ/Баг-репорт.xlsx
+++ b/Мои БАГ-РЕПОРТЫ/Баг-репорт.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hidden\Desktop\Финальный проект_АКАДЕМИЯ ТОП\Мой_ДИПЛОМНЫЙ_ПРОЕКТ\Мои БАГ-РЕПОРТЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D9CF45-80F9-4AFE-B458-1798A6675965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D00C349-41EC-4AAA-BBC0-9C6258C9CBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="174">
   <si>
     <t>№</t>
   </si>
@@ -361,9 +361,6 @@
   </si>
   <si>
     <t>Yandex Browser (Версия 26.4.4.826 (64-bit)</t>
-  </si>
-  <si>
-    <t>Microsoft Edge (Версия 149.0.4022.69</t>
   </si>
   <si>
     <t>Advice 1</t>
@@ -924,7 +921,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1008,17 +1005,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1269,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1009"/>
+  <dimension ref="A1:K1009"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1283,53 +1271,49 @@
     <col min="9" max="9" width="16.5546875" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" customWidth="1"/>
-    <col min="13" max="23" width="8.6640625" customWidth="1"/>
+    <col min="12" max="22" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="31" t="s">
-        <v>7</v>
-      </c>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
     </row>
-    <row r="2" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
+    <row r="2" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="34"/>
       <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
       <c r="I2" s="2" t="s">
         <v>83</v>
       </c>
@@ -1339,15 +1323,12 @@
       <c r="K2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>86</v>
-      </c>
     </row>
-    <row r="3" spans="1:12" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="31" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="19" t="s">
@@ -1363,7 +1344,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>18</v>
@@ -1377,11 +1358,8 @@
       <c r="K3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="15" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="4" spans="1:12" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1415,11 +1393,8 @@
       <c r="K4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="15" t="s">
-        <v>41</v>
-      </c>
     </row>
-    <row r="5" spans="1:12" ht="144.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="144.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1453,11 +1428,8 @@
       <c r="K5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="15" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="6" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1491,11 +1463,8 @@
       <c r="K6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="15" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="7" spans="1:12" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -1529,11 +1498,8 @@
       <c r="K7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L7" s="28" t="s">
-        <v>42</v>
-      </c>
     </row>
-    <row r="8" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1567,11 +1533,8 @@
       <c r="K8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="15" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="9" spans="1:12" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1605,11 +1568,8 @@
       <c r="K9" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>61</v>
-      </c>
     </row>
-    <row r="10" spans="1:12" ht="94.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="94.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1643,11 +1603,8 @@
       <c r="K10" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="11" spans="1:12" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1655,7 +1612,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>10</v>
@@ -1681,11 +1638,8 @@
       <c r="K11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>75</v>
-      </c>
     </row>
-    <row r="12" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1693,7 +1647,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>10</v>
@@ -1719,371 +1673,340 @@
       <c r="K12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>79</v>
-      </c>
     </row>
-    <row r="13" spans="1:12" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="J13" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="J14" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="H15" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="J15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="H17" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="J17" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F18" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="I18" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="J18" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="H19" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="J19" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F20" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="H20" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>164</v>
-      </c>
       <c r="J20" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="43" t="s">
+    <row r="21" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="34"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="38" t="s">
+    <row r="22" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="38" t="s">
+      <c r="F22" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="44" t="s">
+      <c r="I22" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="32" t="s">
-        <v>7</v>
-      </c>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
     </row>
-    <row r="23" spans="1:12" ht="42" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+    <row r="23" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="A23" s="34"/>
       <c r="B23" s="8"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="40"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="37"/>
       <c r="I23" s="9" t="s">
         <v>83</v>
       </c>
@@ -2093,191 +2016,173 @@
       <c r="K23" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="L23" s="9" t="s">
-        <v>86</v>
-      </c>
     </row>
-    <row r="24" spans="1:12" ht="178.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="178.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>1</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F24" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="H24" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>2</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F25" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="H25" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="I25" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>3</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>99</v>
-      </c>
       <c r="I26" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>4</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="G27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="J27" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>5</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="G28" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="H28" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>173</v>
-      </c>
       <c r="I28" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -2289,11 +2194,10 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3273,6 +3177,7 @@
     <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="G22:G23"/>
@@ -3289,7 +3194,6 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
